--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N65_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N65_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.73603876358311</v>
+        <v>7.594606299082256</v>
       </c>
       <c r="D2" t="n">
-        <v>47.1015422456293</v>
+        <v>7.654000614914761</v>
       </c>
       <c r="E2" t="n">
-        <v>8.326363572883134</v>
+        <v>1.353034080593509</v>
       </c>
       <c r="F2" t="n">
-        <v>8.409132622436026</v>
+        <v>1.366484051145854</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>63.27512373672391</v>
+        <v>10.28220760721764</v>
       </c>
       <c r="D3" t="n">
-        <v>31.82583331520998</v>
+        <v>5.171697913721623</v>
       </c>
       <c r="E3" t="n">
-        <v>8.326363572883134</v>
+        <v>1.353034080593509</v>
       </c>
       <c r="F3" t="n">
-        <v>8.409132622436026</v>
+        <v>1.366484051145854</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>47.29515743057627</v>
+        <v>7.685463082468644</v>
       </c>
       <c r="D4" t="n">
-        <v>47.74517364969318</v>
+        <v>7.758590718075141</v>
       </c>
       <c r="E4" t="n">
-        <v>8.326363572883134</v>
+        <v>1.353034080593509</v>
       </c>
       <c r="F4" t="n">
-        <v>8.409132622436026</v>
+        <v>1.366484051145854</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.36368200871608</v>
+        <v>6.396598326416363</v>
       </c>
       <c r="D5" t="n">
-        <v>39.3217229809805</v>
+        <v>6.389779984409332</v>
       </c>
       <c r="E5" t="n">
-        <v>8.326363572883134</v>
+        <v>1.353034080593509</v>
       </c>
       <c r="F5" t="n">
-        <v>8.409132622436026</v>
+        <v>1.366484051145854</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>56.42043838916531</v>
+        <v>9.168321238239363</v>
       </c>
       <c r="D6" t="n">
-        <v>56.69946046614826</v>
+        <v>9.213662325749093</v>
       </c>
       <c r="E6" t="n">
-        <v>8.326363572883134</v>
+        <v>1.353034080593509</v>
       </c>
       <c r="F6" t="n">
-        <v>8.409132622436026</v>
+        <v>1.366484051145854</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
